--- a/artfynd/A 54020-2020 artfynd.xlsx
+++ b/artfynd/A 54020-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54020-2020 artfynd.xlsx
+++ b/artfynd/A 54020-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5466,10 +5466,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>94218311</v>
+        <v>94210923</v>
       </c>
       <c r="B44" t="n">
-        <v>77588</v>
+        <v>77506</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5482,37 +5482,38 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Svedjebodarna, Jmt</t>
+          <t>Berg, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>444498.4269470874</v>
+        <v>444853.6228730685</v>
       </c>
       <c r="R44" t="n">
-        <v>6969809.078205185</v>
+        <v>6969553.698312298</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5566,19 +5567,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>94210923</v>
+        <v>94218331</v>
       </c>
       <c r="B45" t="n">
         <v>77506</v>
@@ -5612,20 +5613,19 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Berg, Jmt</t>
+          <t>Långbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444853.6228730685</v>
+        <v>444503.9554544147</v>
       </c>
       <c r="R45" t="n">
-        <v>6969553.698312298</v>
+        <v>6969541.329734193</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5679,19 +5679,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>94218331</v>
+        <v>94218328</v>
       </c>
       <c r="B46" t="n">
         <v>77506</v>
@@ -5731,10 +5731,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444503.9554544147</v>
+        <v>444875.4450644604</v>
       </c>
       <c r="R46" t="n">
-        <v>6969541.329734193</v>
+        <v>6969572.971996532</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5803,10 +5803,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>94218328</v>
+        <v>94218345</v>
       </c>
       <c r="B47" t="n">
-        <v>77506</v>
+        <v>81236</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5819,21 +5819,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5843,10 +5843,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444875.4450644604</v>
+        <v>444467.4352160227</v>
       </c>
       <c r="R47" t="n">
-        <v>6969572.971996532</v>
+        <v>6969815.540710589</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5897,6 +5897,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5912,119 +5913,6 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>94218345</v>
-      </c>
-      <c r="B48" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Långbodarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q48" t="n">
-        <v>444467.4352160227</v>
-      </c>
-      <c r="R48" t="n">
-        <v>6969815.540710589</v>
-      </c>
-      <c r="S48" t="n">
-        <v>15</v>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>Oviken</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>2021-06-12</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>2021-06-12</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF48" t="inlineStr"/>
-      <c r="AG48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT48" t="inlineStr"/>
-      <c r="AW48" t="inlineStr">
-        <is>
-          <t>Miriam Schenk</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>Miriam Schenk</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
